--- a/artfynd/A 575-2021 artfynd.xlsx
+++ b/artfynd/A 575-2021 artfynd.xlsx
@@ -2868,10 +2868,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119651678</v>
+        <v>119651641</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>91254</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2880,25 +2880,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477860</v>
+        <v>477881</v>
       </c>
       <c r="R23" t="n">
-        <v>7143097</v>
+        <v>7142847</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,11 +2944,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2975,10 +2970,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119651641</v>
+        <v>119651678</v>
       </c>
       <c r="B24" t="n">
-        <v>91254</v>
+        <v>57326</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,25 +2982,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3015,10 +3010,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477881</v>
+        <v>477860</v>
       </c>
       <c r="R24" t="n">
-        <v>7142847</v>
+        <v>7143097</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,6 +3046,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119651706</v>
+        <v>119651670</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3307,34 +3307,50 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478162</v>
+        <v>477861</v>
       </c>
       <c r="R27" t="n">
-        <v>7142400</v>
+        <v>7142701</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3393,10 +3409,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119651639</v>
+        <v>119651706</v>
       </c>
       <c r="B28" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3409,21 +3425,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3433,10 +3449,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478102</v>
+        <v>478162</v>
       </c>
       <c r="R28" t="n">
-        <v>7142644</v>
+        <v>7142400</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,10 +3511,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119651670</v>
+        <v>119651639</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3511,50 +3527,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477861</v>
+        <v>478102</v>
       </c>
       <c r="R29" t="n">
-        <v>7142701</v>
+        <v>7142644</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3720,10 +3720,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119651638</v>
+        <v>119651704</v>
       </c>
       <c r="B31" t="n">
-        <v>87406</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3736,21 +3736,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478188</v>
+        <v>478040</v>
       </c>
       <c r="R31" t="n">
-        <v>7142387</v>
+        <v>7142457</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119651704</v>
+        <v>119651638</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>87406</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3838,21 +3838,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478040</v>
+        <v>478188</v>
       </c>
       <c r="R32" t="n">
-        <v>7142457</v>
+        <v>7142387</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119651681</v>
+        <v>119651679</v>
       </c>
       <c r="B35" t="n">
-        <v>79607</v>
+        <v>57326</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4149,21 +4149,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478033</v>
+        <v>477695</v>
       </c>
       <c r="R35" t="n">
-        <v>7142718</v>
+        <v>7143155</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4209,6 +4209,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4235,10 +4240,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651679</v>
+        <v>119651690</v>
       </c>
       <c r="B36" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4251,21 +4256,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4275,10 +4280,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477695</v>
+        <v>478032</v>
       </c>
       <c r="R36" t="n">
-        <v>7143155</v>
+        <v>7142707</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4311,11 +4316,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4342,10 +4342,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119651690</v>
+        <v>119651698</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4358,21 +4358,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4382,10 +4382,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478032</v>
+        <v>477862</v>
       </c>
       <c r="R37" t="n">
-        <v>7142707</v>
+        <v>7142754</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4444,10 +4444,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119651698</v>
+        <v>119651645</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4456,25 +4456,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4484,10 +4484,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477862</v>
+        <v>478034</v>
       </c>
       <c r="R38" t="n">
-        <v>7142754</v>
+        <v>7142532</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4546,10 +4546,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119651645</v>
+        <v>119651685</v>
       </c>
       <c r="B39" t="n">
-        <v>91254</v>
+        <v>90558</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4558,25 +4558,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478034</v>
+        <v>478272</v>
       </c>
       <c r="R39" t="n">
-        <v>7142532</v>
+        <v>7142513</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4648,10 +4648,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119651685</v>
+        <v>119651681</v>
       </c>
       <c r="B40" t="n">
-        <v>90558</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4664,21 +4664,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478272</v>
+        <v>478033</v>
       </c>
       <c r="R40" t="n">
-        <v>7142513</v>
+        <v>7142718</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5383,10 +5383,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119651700</v>
+        <v>119651664</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5399,21 +5399,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477768</v>
+        <v>478157</v>
       </c>
       <c r="R47" t="n">
-        <v>7142610</v>
+        <v>7142616</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5459,6 +5459,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5485,10 +5490,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119651664</v>
+        <v>119651700</v>
       </c>
       <c r="B48" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5501,21 +5506,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5525,10 +5530,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478157</v>
+        <v>477768</v>
       </c>
       <c r="R48" t="n">
-        <v>7142616</v>
+        <v>7142610</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5561,11 +5566,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 575-2021 artfynd.xlsx
+++ b/artfynd/A 575-2021 artfynd.xlsx
@@ -2868,10 +2868,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119651641</v>
+        <v>119651678</v>
       </c>
       <c r="B23" t="n">
-        <v>91254</v>
+        <v>57326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2880,25 +2880,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477881</v>
+        <v>477860</v>
       </c>
       <c r="R23" t="n">
-        <v>7142847</v>
+        <v>7143097</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,6 +2944,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2970,10 +2975,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119651678</v>
+        <v>119651641</v>
       </c>
       <c r="B24" t="n">
-        <v>57326</v>
+        <v>91254</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2982,25 +2987,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3010,10 +3015,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477860</v>
+        <v>477881</v>
       </c>
       <c r="R24" t="n">
-        <v>7143097</v>
+        <v>7142847</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,11 +3051,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4133,10 +4133,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119651679</v>
+        <v>119651681</v>
       </c>
       <c r="B35" t="n">
-        <v>57326</v>
+        <v>79607</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4149,21 +4149,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477695</v>
+        <v>478033</v>
       </c>
       <c r="R35" t="n">
-        <v>7143155</v>
+        <v>7142718</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4209,11 +4209,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4240,10 +4235,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651690</v>
+        <v>119651679</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>57326</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4256,21 +4251,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4280,10 +4275,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478032</v>
+        <v>477695</v>
       </c>
       <c r="R36" t="n">
-        <v>7142707</v>
+        <v>7143155</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4316,6 +4311,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4342,10 +4342,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119651698</v>
+        <v>119651690</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4358,21 +4358,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4382,10 +4382,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477862</v>
+        <v>478032</v>
       </c>
       <c r="R37" t="n">
-        <v>7142754</v>
+        <v>7142707</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4444,10 +4444,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119651645</v>
+        <v>119651698</v>
       </c>
       <c r="B38" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4456,25 +4456,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4484,10 +4484,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478034</v>
+        <v>477862</v>
       </c>
       <c r="R38" t="n">
-        <v>7142532</v>
+        <v>7142754</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4546,10 +4546,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119651685</v>
+        <v>119651645</v>
       </c>
       <c r="B39" t="n">
-        <v>90558</v>
+        <v>91254</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4558,25 +4558,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478272</v>
+        <v>478034</v>
       </c>
       <c r="R39" t="n">
-        <v>7142513</v>
+        <v>7142532</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4648,10 +4648,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119651681</v>
+        <v>119651685</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>90558</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4664,21 +4664,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478033</v>
+        <v>478272</v>
       </c>
       <c r="R40" t="n">
-        <v>7142718</v>
+        <v>7142513</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 575-2021 artfynd.xlsx
+++ b/artfynd/A 575-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651676</v>
+        <v>119651706</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478329</v>
+        <v>478162</v>
       </c>
       <c r="R2" t="n">
-        <v>7142297</v>
+        <v>7142400</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651709</v>
+        <v>119651685</v>
       </c>
       <c r="B3" t="n">
-        <v>91128</v>
+        <v>90558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478183</v>
+        <v>478272</v>
       </c>
       <c r="R3" t="n">
-        <v>7142390</v>
+        <v>7142513</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651688</v>
+        <v>119651705</v>
       </c>
       <c r="B4" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477825</v>
+        <v>478087</v>
       </c>
       <c r="R4" t="n">
-        <v>7143049</v>
+        <v>7142484</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119651680</v>
+        <v>119651694</v>
       </c>
       <c r="B5" t="n">
-        <v>79608</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477977</v>
+        <v>477874</v>
       </c>
       <c r="R5" t="n">
-        <v>7142600</v>
+        <v>7142867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651699</v>
+        <v>119651671</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477616</v>
+        <v>478034</v>
       </c>
       <c r="R6" t="n">
-        <v>7142666</v>
+        <v>7142454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651695</v>
+        <v>119651641</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>91254</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477953</v>
+        <v>477881</v>
       </c>
       <c r="R7" t="n">
-        <v>7142946</v>
+        <v>7142847</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651696</v>
+        <v>119651682</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>57421</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,38 +1304,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478181</v>
+        <v>477848</v>
       </c>
       <c r="R8" t="n">
-        <v>7142430</v>
+        <v>7142542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651691</v>
+        <v>119651642</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>91254</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1422,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477857</v>
+        <v>477886</v>
       </c>
       <c r="R9" t="n">
-        <v>7142825</v>
+        <v>7142880</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651683</v>
+        <v>119651707</v>
       </c>
       <c r="B10" t="n">
-        <v>57421</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,54 +1524,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478354</v>
+        <v>478303</v>
       </c>
       <c r="R10" t="n">
-        <v>7142310</v>
+        <v>7142341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,10 +1614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651644</v>
+        <v>119651697</v>
       </c>
       <c r="B11" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1626,25 +1626,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477632</v>
+        <v>478297</v>
       </c>
       <c r="R11" t="n">
-        <v>7142733</v>
+        <v>7142499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651708</v>
+        <v>119651676</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,21 +1732,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478398</v>
+        <v>478329</v>
       </c>
       <c r="R12" t="n">
-        <v>7142260</v>
+        <v>7142297</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,6 +1792,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1818,10 +1823,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651707</v>
+        <v>119651677</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,21 +1839,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1858,10 +1863,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478303</v>
+        <v>478328</v>
       </c>
       <c r="R13" t="n">
-        <v>7142341</v>
+        <v>7142289</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,6 +1899,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,7 +1930,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651667</v>
+        <v>119651674</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -1960,10 +1970,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477770</v>
+        <v>478153</v>
       </c>
       <c r="R14" t="n">
-        <v>7143140</v>
+        <v>7142438</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,7 +2010,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2027,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651671</v>
+        <v>119651696</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,21 +2053,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2067,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478034</v>
+        <v>478181</v>
       </c>
       <c r="R15" t="n">
-        <v>7142454</v>
+        <v>7142430</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,11 +2113,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2134,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119651687</v>
+        <v>119651691</v>
       </c>
       <c r="B16" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2150,21 +2155,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2174,10 +2179,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477885</v>
+        <v>477857</v>
       </c>
       <c r="R16" t="n">
-        <v>7142877</v>
+        <v>7142825</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2236,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119651702</v>
+        <v>119651678</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2252,21 +2257,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2281,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477946</v>
+        <v>477860</v>
       </c>
       <c r="R17" t="n">
-        <v>7142571</v>
+        <v>7143097</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,6 +2317,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2338,10 +2348,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119651697</v>
+        <v>119651679</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2354,21 +2364,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2378,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478297</v>
+        <v>477695</v>
       </c>
       <c r="R18" t="n">
-        <v>7142499</v>
+        <v>7143155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,6 +2424,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2440,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119651705</v>
+        <v>119651688</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2456,21 +2471,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2480,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478087</v>
+        <v>477825</v>
       </c>
       <c r="R19" t="n">
-        <v>7142484</v>
+        <v>7143049</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119651675</v>
+        <v>119651690</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2558,54 +2573,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478361</v>
+        <v>478032</v>
       </c>
       <c r="R20" t="n">
-        <v>7142354</v>
+        <v>7142707</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119651701</v>
+        <v>119651695</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2680,21 +2675,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2704,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477873</v>
+        <v>477953</v>
       </c>
       <c r="R21" t="n">
-        <v>7142534</v>
+        <v>7142946</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2766,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119651689</v>
+        <v>119651680</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>79608</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2782,21 +2777,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2806,10 +2801,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478214</v>
+        <v>477977</v>
       </c>
       <c r="R22" t="n">
-        <v>7142533</v>
+        <v>7142600</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2868,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119651678</v>
+        <v>119651704</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2884,21 +2879,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2908,10 +2903,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477860</v>
+        <v>478040</v>
       </c>
       <c r="R23" t="n">
-        <v>7143097</v>
+        <v>7142457</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,11 +2939,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2975,10 +2965,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119651641</v>
+        <v>119651666</v>
       </c>
       <c r="B24" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,25 +2977,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3015,10 +3005,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477881</v>
+        <v>477775</v>
       </c>
       <c r="R24" t="n">
-        <v>7142847</v>
+        <v>7143155</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,6 +3041,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3184,10 +3179,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119651674</v>
+        <v>119651646</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3196,25 +3191,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3224,10 +3219,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478153</v>
+        <v>478074</v>
       </c>
       <c r="R26" t="n">
-        <v>7142438</v>
+        <v>7142501</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,11 +3255,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3291,10 +3281,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119651670</v>
+        <v>119651698</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3307,50 +3297,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477861</v>
+        <v>477862</v>
       </c>
       <c r="R27" t="n">
-        <v>7142701</v>
+        <v>7142754</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,10 +3383,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119651706</v>
+        <v>119651665</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3425,21 +3399,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478162</v>
+        <v>477656</v>
       </c>
       <c r="R28" t="n">
-        <v>7142400</v>
+        <v>7143131</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3511,10 +3485,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119651639</v>
+        <v>119651638</v>
       </c>
       <c r="B29" t="n">
-        <v>90562</v>
+        <v>87406</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3527,21 +3501,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>4412</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3551,10 +3525,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478102</v>
+        <v>478188</v>
       </c>
       <c r="R29" t="n">
-        <v>7142644</v>
+        <v>7142387</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3613,10 +3587,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119651669</v>
+        <v>119651701</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3629,21 +3603,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3653,10 +3627,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477624</v>
+        <v>477873</v>
       </c>
       <c r="R30" t="n">
-        <v>7142669</v>
+        <v>7142534</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3689,11 +3663,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3720,10 +3689,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119651704</v>
+        <v>119651669</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3736,21 +3705,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3760,10 +3729,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478040</v>
+        <v>477624</v>
       </c>
       <c r="R31" t="n">
-        <v>7142457</v>
+        <v>7142669</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3796,6 +3765,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3822,10 +3796,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119651638</v>
+        <v>119651699</v>
       </c>
       <c r="B32" t="n">
-        <v>87406</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3838,21 +3812,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3862,10 +3836,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478188</v>
+        <v>477616</v>
       </c>
       <c r="R32" t="n">
-        <v>7142387</v>
+        <v>7142666</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,10 +3898,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119651666</v>
+        <v>119651683</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3936,20 +3910,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3957,17 +3931,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477775</v>
+        <v>478354</v>
       </c>
       <c r="R33" t="n">
-        <v>7143155</v>
+        <v>7142310</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4000,11 +3990,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4031,10 +4016,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119651646</v>
+        <v>119651670</v>
       </c>
       <c r="B34" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4043,38 +4028,54 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478074</v>
+        <v>477861</v>
       </c>
       <c r="R34" t="n">
-        <v>7142501</v>
+        <v>7142701</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4133,10 +4134,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119651681</v>
+        <v>119651709</v>
       </c>
       <c r="B35" t="n">
-        <v>79607</v>
+        <v>91128</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4145,25 +4146,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4173,10 +4174,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478033</v>
+        <v>478183</v>
       </c>
       <c r="R35" t="n">
-        <v>7142718</v>
+        <v>7142390</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4235,10 +4236,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651679</v>
+        <v>119651664</v>
       </c>
       <c r="B36" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4251,16 +4252,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4275,10 +4276,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477695</v>
+        <v>478157</v>
       </c>
       <c r="R36" t="n">
-        <v>7143155</v>
+        <v>7142616</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4315,7 +4316,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4342,10 +4343,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119651690</v>
+        <v>119651643</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>91254</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4354,25 +4355,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4382,10 +4383,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478032</v>
+        <v>477621</v>
       </c>
       <c r="R37" t="n">
-        <v>7142707</v>
+        <v>7142895</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4444,10 +4445,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119651698</v>
+        <v>119651689</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4460,21 +4461,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4484,10 +4485,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477862</v>
+        <v>478214</v>
       </c>
       <c r="R38" t="n">
-        <v>7142754</v>
+        <v>7142533</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4546,10 +4547,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119651645</v>
+        <v>119651639</v>
       </c>
       <c r="B39" t="n">
-        <v>91254</v>
+        <v>90562</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4558,25 +4559,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4586,10 +4587,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478034</v>
+        <v>478102</v>
       </c>
       <c r="R39" t="n">
-        <v>7142532</v>
+        <v>7142644</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4648,10 +4649,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119651685</v>
+        <v>119651645</v>
       </c>
       <c r="B40" t="n">
-        <v>90558</v>
+        <v>91254</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4660,25 +4661,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4688,10 +4689,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478272</v>
+        <v>478034</v>
       </c>
       <c r="R40" t="n">
-        <v>7142513</v>
+        <v>7142532</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4750,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119651694</v>
+        <v>119651700</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4766,21 +4767,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4790,10 +4791,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477874</v>
+        <v>477768</v>
       </c>
       <c r="R41" t="n">
-        <v>7142867</v>
+        <v>7142610</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4852,10 +4853,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119651642</v>
+        <v>119651702</v>
       </c>
       <c r="B42" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4864,25 +4865,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4892,10 +4893,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477886</v>
+        <v>477946</v>
       </c>
       <c r="R42" t="n">
-        <v>7142880</v>
+        <v>7142571</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4954,10 +4955,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119651643</v>
+        <v>119651687</v>
       </c>
       <c r="B43" t="n">
-        <v>91254</v>
+        <v>90558</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4966,25 +4967,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4994,10 +4995,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477621</v>
+        <v>477885</v>
       </c>
       <c r="R43" t="n">
-        <v>7142895</v>
+        <v>7142877</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5056,10 +5057,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119651682</v>
+        <v>119651708</v>
       </c>
       <c r="B44" t="n">
-        <v>57421</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5068,54 +5069,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477848</v>
+        <v>478398</v>
       </c>
       <c r="R44" t="n">
-        <v>7142542</v>
+        <v>7142260</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5174,7 +5159,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119651665</v>
+        <v>119651675</v>
       </c>
       <c r="B45" t="n">
         <v>57310</v>
@@ -5207,17 +5192,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477656</v>
+        <v>478361</v>
       </c>
       <c r="R45" t="n">
-        <v>7143131</v>
+        <v>7142354</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5276,10 +5281,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119651677</v>
+        <v>119651644</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5288,25 +5293,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5316,10 +5321,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478328</v>
+        <v>477632</v>
       </c>
       <c r="R46" t="n">
-        <v>7142289</v>
+        <v>7142733</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5352,11 +5357,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119651664</v>
+        <v>119651681</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5399,21 +5399,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478157</v>
+        <v>478033</v>
       </c>
       <c r="R47" t="n">
-        <v>7142616</v>
+        <v>7142718</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5459,11 +5459,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5490,10 +5485,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119651700</v>
+        <v>119651667</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5506,21 +5501,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5530,10 +5525,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477768</v>
+        <v>477770</v>
       </c>
       <c r="R48" t="n">
-        <v>7142610</v>
+        <v>7143140</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5566,6 +5561,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 575-2021 artfynd.xlsx
+++ b/artfynd/A 575-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651706</v>
+        <v>119651698</v>
       </c>
       <c r="B2" t="n">
         <v>78526</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478162</v>
+        <v>477862</v>
       </c>
       <c r="R2" t="n">
-        <v>7142400</v>
+        <v>7142754</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651685</v>
+        <v>119651646</v>
       </c>
       <c r="B3" t="n">
-        <v>90558</v>
+        <v>91254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478272</v>
+        <v>478074</v>
       </c>
       <c r="R3" t="n">
-        <v>7142513</v>
+        <v>7142501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651705</v>
+        <v>119651687</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478087</v>
+        <v>477885</v>
       </c>
       <c r="R4" t="n">
-        <v>7142484</v>
+        <v>7142877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119651694</v>
+        <v>119651676</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477874</v>
+        <v>478329</v>
       </c>
       <c r="R5" t="n">
-        <v>7142867</v>
+        <v>7142297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651671</v>
+        <v>119651701</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478034</v>
+        <v>477873</v>
       </c>
       <c r="R6" t="n">
-        <v>7142454</v>
+        <v>7142534</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651641</v>
+        <v>119651697</v>
       </c>
       <c r="B7" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477881</v>
+        <v>478297</v>
       </c>
       <c r="R7" t="n">
-        <v>7142847</v>
+        <v>7142499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651682</v>
+        <v>119651675</v>
       </c>
       <c r="B8" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,20 +1304,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1327,11 +1327,15 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1348,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477848</v>
+        <v>478361</v>
       </c>
       <c r="R8" t="n">
-        <v>7142542</v>
+        <v>7142354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651642</v>
+        <v>119651705</v>
       </c>
       <c r="B9" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1422,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1450,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477886</v>
+        <v>478087</v>
       </c>
       <c r="R9" t="n">
-        <v>7142880</v>
+        <v>7142484</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651707</v>
+        <v>119651683</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>57421</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1524,38 +1528,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478303</v>
+        <v>478354</v>
       </c>
       <c r="R10" t="n">
-        <v>7142341</v>
+        <v>7142310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651697</v>
+        <v>119651709</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>91128</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1626,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478297</v>
+        <v>478183</v>
       </c>
       <c r="R11" t="n">
-        <v>7142499</v>
+        <v>7142390</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651676</v>
+        <v>119651689</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478329</v>
+        <v>478214</v>
       </c>
       <c r="R12" t="n">
-        <v>7142297</v>
+        <v>7142533</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,11 +1812,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,7 +1838,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651677</v>
+        <v>119651667</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1863,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478328</v>
+        <v>477770</v>
       </c>
       <c r="R13" t="n">
-        <v>7142289</v>
+        <v>7143140</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,7 +1918,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,7 +1945,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651674</v>
+        <v>119651664</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -1970,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478153</v>
+        <v>478157</v>
       </c>
       <c r="R14" t="n">
-        <v>7142438</v>
+        <v>7142616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,7 +2025,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2037,10 +2052,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651696</v>
+        <v>119651704</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2053,21 +2068,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2077,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478181</v>
+        <v>478040</v>
       </c>
       <c r="R15" t="n">
-        <v>7142430</v>
+        <v>7142457</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,7 +2154,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119651691</v>
+        <v>119651695</v>
       </c>
       <c r="B16" t="n">
         <v>90580</v>
@@ -2179,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477857</v>
+        <v>477953</v>
       </c>
       <c r="R16" t="n">
-        <v>7142825</v>
+        <v>7142946</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119651678</v>
+        <v>119651691</v>
       </c>
       <c r="B17" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2257,21 +2272,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2281,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477860</v>
+        <v>477857</v>
       </c>
       <c r="R17" t="n">
-        <v>7143097</v>
+        <v>7142825</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,11 +2332,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2348,10 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119651679</v>
+        <v>119651642</v>
       </c>
       <c r="B18" t="n">
-        <v>57326</v>
+        <v>91254</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2360,25 +2370,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2388,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477695</v>
+        <v>477886</v>
       </c>
       <c r="R18" t="n">
-        <v>7143155</v>
+        <v>7142880</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,11 +2434,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2455,10 +2460,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119651688</v>
+        <v>119651677</v>
       </c>
       <c r="B19" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,21 +2476,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2495,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477825</v>
+        <v>478328</v>
       </c>
       <c r="R19" t="n">
-        <v>7143049</v>
+        <v>7142289</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,6 +2536,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2557,10 +2567,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119651690</v>
+        <v>119651702</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2573,21 +2583,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2607,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478032</v>
+        <v>477946</v>
       </c>
       <c r="R20" t="n">
-        <v>7142707</v>
+        <v>7142571</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,10 +2669,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119651695</v>
+        <v>119651671</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,21 +2685,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2709,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477953</v>
+        <v>478034</v>
       </c>
       <c r="R21" t="n">
-        <v>7142946</v>
+        <v>7142454</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,6 +2745,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2761,10 +2776,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119651680</v>
+        <v>119651688</v>
       </c>
       <c r="B22" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2777,21 +2792,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2801,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477977</v>
+        <v>477825</v>
       </c>
       <c r="R22" t="n">
-        <v>7142600</v>
+        <v>7143049</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,10 +2878,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119651704</v>
+        <v>119651681</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2879,21 +2894,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2903,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478040</v>
+        <v>478033</v>
       </c>
       <c r="R23" t="n">
-        <v>7142457</v>
+        <v>7142718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3072,10 +3087,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119651668</v>
+        <v>119651699</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3088,21 +3103,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3112,10 +3127,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477695</v>
+        <v>477616</v>
       </c>
       <c r="R25" t="n">
-        <v>7142939</v>
+        <v>7142666</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,11 +3163,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3179,10 +3189,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119651646</v>
+        <v>119651670</v>
       </c>
       <c r="B26" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3191,38 +3201,54 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478074</v>
+        <v>477861</v>
       </c>
       <c r="R26" t="n">
-        <v>7142501</v>
+        <v>7142701</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3307,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119651698</v>
+        <v>119651700</v>
       </c>
       <c r="B27" t="n">
         <v>78526</v>
@@ -3321,10 +3347,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477862</v>
+        <v>477768</v>
       </c>
       <c r="R27" t="n">
-        <v>7142754</v>
+        <v>7142610</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3383,10 +3409,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119651665</v>
+        <v>119651638</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>87406</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3399,21 +3425,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3423,10 +3449,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477656</v>
+        <v>478188</v>
       </c>
       <c r="R28" t="n">
-        <v>7143131</v>
+        <v>7142387</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,10 +3511,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119651638</v>
+        <v>119651665</v>
       </c>
       <c r="B29" t="n">
-        <v>87406</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3501,21 +3527,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3525,10 +3551,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478188</v>
+        <v>477656</v>
       </c>
       <c r="R29" t="n">
-        <v>7142387</v>
+        <v>7143131</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3587,10 +3613,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119651701</v>
+        <v>119651674</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3603,21 +3629,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3627,10 +3653,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477873</v>
+        <v>478153</v>
       </c>
       <c r="R30" t="n">
-        <v>7142534</v>
+        <v>7142438</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3663,6 +3689,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3689,10 +3720,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119651669</v>
+        <v>119651708</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3705,21 +3736,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3729,10 +3760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477624</v>
+        <v>478398</v>
       </c>
       <c r="R31" t="n">
-        <v>7142669</v>
+        <v>7142260</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3765,11 +3796,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3796,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119651699</v>
+        <v>119651696</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3812,21 +3838,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3836,10 +3862,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477616</v>
+        <v>478181</v>
       </c>
       <c r="R32" t="n">
-        <v>7142666</v>
+        <v>7142430</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3898,10 +3924,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119651683</v>
+        <v>119651694</v>
       </c>
       <c r="B33" t="n">
-        <v>57421</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3910,54 +3936,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478354</v>
+        <v>477874</v>
       </c>
       <c r="R33" t="n">
-        <v>7142310</v>
+        <v>7142867</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4016,10 +4026,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119651670</v>
+        <v>119651706</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4032,50 +4042,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477861</v>
+        <v>478162</v>
       </c>
       <c r="R34" t="n">
-        <v>7142701</v>
+        <v>7142400</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4134,10 +4128,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119651709</v>
+        <v>119651678</v>
       </c>
       <c r="B35" t="n">
-        <v>91128</v>
+        <v>57326</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4146,25 +4140,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>760</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4174,10 +4168,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478183</v>
+        <v>477860</v>
       </c>
       <c r="R35" t="n">
-        <v>7142390</v>
+        <v>7143097</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4210,6 +4204,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4236,10 +4235,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651664</v>
+        <v>119651690</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4252,21 +4251,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4276,10 +4275,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478157</v>
+        <v>478032</v>
       </c>
       <c r="R36" t="n">
-        <v>7142616</v>
+        <v>7142707</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4312,11 +4311,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4343,10 +4337,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119651643</v>
+        <v>119651639</v>
       </c>
       <c r="B37" t="n">
-        <v>91254</v>
+        <v>90562</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4355,25 +4349,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4383,10 +4377,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477621</v>
+        <v>478102</v>
       </c>
       <c r="R37" t="n">
-        <v>7142895</v>
+        <v>7142644</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4445,10 +4439,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119651689</v>
+        <v>119651680</v>
       </c>
       <c r="B38" t="n">
-        <v>90580</v>
+        <v>79608</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4461,21 +4455,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,10 +4479,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478214</v>
+        <v>477977</v>
       </c>
       <c r="R38" t="n">
-        <v>7142533</v>
+        <v>7142600</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4547,10 +4541,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119651639</v>
+        <v>119651641</v>
       </c>
       <c r="B39" t="n">
-        <v>90562</v>
+        <v>91254</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4559,25 +4553,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4587,10 +4581,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478102</v>
+        <v>477881</v>
       </c>
       <c r="R39" t="n">
-        <v>7142644</v>
+        <v>7142847</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4751,10 +4745,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119651700</v>
+        <v>119651669</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4767,21 +4761,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4791,10 +4785,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477768</v>
+        <v>477624</v>
       </c>
       <c r="R41" t="n">
-        <v>7142610</v>
+        <v>7142669</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4827,6 +4821,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4853,10 +4852,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119651702</v>
+        <v>119651668</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4869,21 +4868,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4893,10 +4892,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477946</v>
+        <v>477695</v>
       </c>
       <c r="R42" t="n">
-        <v>7142571</v>
+        <v>7142939</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4929,6 +4928,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4955,10 +4959,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119651687</v>
+        <v>119651679</v>
       </c>
       <c r="B43" t="n">
-        <v>90558</v>
+        <v>57326</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4971,21 +4975,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4995,10 +4999,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477885</v>
+        <v>477695</v>
       </c>
       <c r="R43" t="n">
-        <v>7142877</v>
+        <v>7143155</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5031,6 +5035,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5057,10 +5066,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119651708</v>
+        <v>119651643</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5069,25 +5078,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5097,10 +5106,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478398</v>
+        <v>477621</v>
       </c>
       <c r="R44" t="n">
-        <v>7142260</v>
+        <v>7142895</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5159,10 +5168,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119651675</v>
+        <v>119651644</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5171,58 +5180,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478361</v>
+        <v>477632</v>
       </c>
       <c r="R45" t="n">
-        <v>7142354</v>
+        <v>7142733</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5281,10 +5270,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119651644</v>
+        <v>119651707</v>
       </c>
       <c r="B46" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5293,25 +5282,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5321,10 +5310,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477632</v>
+        <v>478303</v>
       </c>
       <c r="R46" t="n">
-        <v>7142733</v>
+        <v>7142341</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5383,10 +5372,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119651681</v>
+        <v>119651685</v>
       </c>
       <c r="B47" t="n">
-        <v>79607</v>
+        <v>90558</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5399,21 +5388,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5423,10 +5412,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478033</v>
+        <v>478272</v>
       </c>
       <c r="R47" t="n">
-        <v>7142718</v>
+        <v>7142513</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5485,10 +5474,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119651667</v>
+        <v>119651682</v>
       </c>
       <c r="B48" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5497,20 +5486,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5518,17 +5507,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477770</v>
+        <v>477848</v>
       </c>
       <c r="R48" t="n">
-        <v>7143140</v>
+        <v>7142542</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5561,11 +5566,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 575-2021 artfynd.xlsx
+++ b/artfynd/A 575-2021 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651646</v>
+        <v>119651687</v>
       </c>
       <c r="B3" t="n">
-        <v>91254</v>
+        <v>90558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478074</v>
+        <v>477885</v>
       </c>
       <c r="R3" t="n">
-        <v>7142501</v>
+        <v>7142877</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651687</v>
+        <v>119651646</v>
       </c>
       <c r="B4" t="n">
-        <v>90558</v>
+        <v>91254</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477885</v>
+        <v>478074</v>
       </c>
       <c r="R4" t="n">
-        <v>7142877</v>
+        <v>7142501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651675</v>
+        <v>119651705</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,54 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478361</v>
+        <v>478087</v>
       </c>
       <c r="R8" t="n">
-        <v>7142354</v>
+        <v>7142484</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651705</v>
+        <v>119651675</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,34 +1410,54 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478087</v>
+        <v>478361</v>
       </c>
       <c r="R9" t="n">
-        <v>7142484</v>
+        <v>7142354</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119651643</v>
+        <v>119651644</v>
       </c>
       <c r="B44" t="n">
         <v>91254</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477621</v>
+        <v>477632</v>
       </c>
       <c r="R44" t="n">
-        <v>7142895</v>
+        <v>7142733</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5168,7 +5168,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119651644</v>
+        <v>119651643</v>
       </c>
       <c r="B45" t="n">
         <v>91254</v>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477632</v>
+        <v>477621</v>
       </c>
       <c r="R45" t="n">
-        <v>7142733</v>
+        <v>7142895</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 575-2021 artfynd.xlsx
+++ b/artfynd/A 575-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651698</v>
+        <v>119651669</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477862</v>
+        <v>477624</v>
       </c>
       <c r="R2" t="n">
-        <v>7142754</v>
+        <v>7142669</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651687</v>
+        <v>119651678</v>
       </c>
       <c r="B3" t="n">
-        <v>90558</v>
+        <v>57326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477885</v>
+        <v>477860</v>
       </c>
       <c r="R3" t="n">
-        <v>7142877</v>
+        <v>7143097</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651646</v>
+        <v>119651638</v>
       </c>
       <c r="B4" t="n">
-        <v>91254</v>
+        <v>87406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478074</v>
+        <v>478188</v>
       </c>
       <c r="R4" t="n">
-        <v>7142501</v>
+        <v>7142387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119651676</v>
+        <v>119651644</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478329</v>
+        <v>477632</v>
       </c>
       <c r="R5" t="n">
-        <v>7142297</v>
+        <v>7142733</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651701</v>
+        <v>119651709</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>91128</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477873</v>
+        <v>478183</v>
       </c>
       <c r="R6" t="n">
-        <v>7142534</v>
+        <v>7142390</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651697</v>
+        <v>119651708</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478297</v>
+        <v>478398</v>
       </c>
       <c r="R7" t="n">
-        <v>7142499</v>
+        <v>7142260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651705</v>
+        <v>119651707</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478087</v>
+        <v>478303</v>
       </c>
       <c r="R8" t="n">
-        <v>7142484</v>
+        <v>7142341</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651675</v>
+        <v>119651667</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1427,37 +1432,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478361</v>
+        <v>477770</v>
       </c>
       <c r="R9" t="n">
-        <v>7142354</v>
+        <v>7143140</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651683</v>
+        <v>119651665</v>
       </c>
       <c r="B10" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,20 +1518,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1549,33 +1539,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478354</v>
+        <v>477656</v>
       </c>
       <c r="R10" t="n">
-        <v>7142310</v>
+        <v>7143131</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651709</v>
+        <v>119651668</v>
       </c>
       <c r="B11" t="n">
-        <v>91128</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478183</v>
+        <v>477695</v>
       </c>
       <c r="R11" t="n">
-        <v>7142390</v>
+        <v>7142939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,6 +1684,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1736,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651689</v>
+        <v>119651679</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>57326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478214</v>
+        <v>477695</v>
       </c>
       <c r="R12" t="n">
-        <v>7142533</v>
+        <v>7143155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651667</v>
+        <v>119651705</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477770</v>
+        <v>478087</v>
       </c>
       <c r="R13" t="n">
-        <v>7143140</v>
+        <v>7142484</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651664</v>
+        <v>119651699</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478157</v>
+        <v>477616</v>
       </c>
       <c r="R14" t="n">
-        <v>7142616</v>
+        <v>7142666</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,11 +2000,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2052,7 +2026,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651704</v>
+        <v>119651702</v>
       </c>
       <c r="B15" t="n">
         <v>78526</v>
@@ -2092,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478040</v>
+        <v>477946</v>
       </c>
       <c r="R15" t="n">
-        <v>7142457</v>
+        <v>7142571</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119651695</v>
+        <v>119651681</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477953</v>
+        <v>478033</v>
       </c>
       <c r="R16" t="n">
-        <v>7142946</v>
+        <v>7142718</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119651691</v>
+        <v>119651685</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2272,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2296,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477857</v>
+        <v>478272</v>
       </c>
       <c r="R17" t="n">
-        <v>7142825</v>
+        <v>7142513</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119651642</v>
+        <v>119651701</v>
       </c>
       <c r="B18" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2398,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477886</v>
+        <v>477873</v>
       </c>
       <c r="R18" t="n">
-        <v>7142880</v>
+        <v>7142534</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2460,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119651677</v>
+        <v>119651683</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2472,20 +2446,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2493,17 +2467,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478328</v>
+        <v>478354</v>
       </c>
       <c r="R19" t="n">
-        <v>7142289</v>
+        <v>7142310</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,11 +2526,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2567,7 +2552,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119651702</v>
+        <v>119651704</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2607,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477946</v>
+        <v>478040</v>
       </c>
       <c r="R20" t="n">
-        <v>7142571</v>
+        <v>7142457</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119651688</v>
+        <v>119651664</v>
       </c>
       <c r="B22" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2792,21 +2777,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2801,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477825</v>
+        <v>478157</v>
       </c>
       <c r="R22" t="n">
-        <v>7143049</v>
+        <v>7142616</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2852,6 +2837,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2878,10 +2868,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119651681</v>
+        <v>119651639</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2894,21 +2884,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2918,10 +2908,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478033</v>
+        <v>478102</v>
       </c>
       <c r="R23" t="n">
-        <v>7142718</v>
+        <v>7142644</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,10 +2970,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119651666</v>
+        <v>119651687</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,21 +2986,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3020,10 +3010,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477775</v>
+        <v>477885</v>
       </c>
       <c r="R24" t="n">
-        <v>7143155</v>
+        <v>7142877</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3056,11 +3046,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3087,10 +3072,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119651699</v>
+        <v>119651675</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3103,34 +3088,54 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477616</v>
+        <v>478361</v>
       </c>
       <c r="R25" t="n">
-        <v>7142666</v>
+        <v>7142354</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3189,7 +3194,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119651670</v>
+        <v>119651666</v>
       </c>
       <c r="B26" t="n">
         <v>57310</v>
@@ -3222,33 +3227,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477861</v>
+        <v>477775</v>
       </c>
       <c r="R26" t="n">
-        <v>7142701</v>
+        <v>7143155</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,6 +3270,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3307,10 +3301,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119651700</v>
+        <v>119651642</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3319,25 +3313,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3347,10 +3341,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477768</v>
+        <v>477886</v>
       </c>
       <c r="R27" t="n">
-        <v>7142610</v>
+        <v>7142880</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,10 +3403,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119651638</v>
+        <v>119651695</v>
       </c>
       <c r="B28" t="n">
-        <v>87406</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3425,21 +3419,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4412</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3443,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478188</v>
+        <v>477953</v>
       </c>
       <c r="R28" t="n">
-        <v>7142387</v>
+        <v>7142946</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3511,10 +3505,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119651665</v>
+        <v>119651700</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3527,21 +3521,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3551,10 +3545,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477656</v>
+        <v>477768</v>
       </c>
       <c r="R29" t="n">
-        <v>7143131</v>
+        <v>7142610</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3613,7 +3607,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119651674</v>
+        <v>119651677</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3653,10 +3647,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478153</v>
+        <v>478328</v>
       </c>
       <c r="R30" t="n">
-        <v>7142438</v>
+        <v>7142289</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3693,7 +3687,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3720,10 +3714,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119651708</v>
+        <v>119651689</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3736,21 +3730,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3760,10 +3754,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478398</v>
+        <v>478214</v>
       </c>
       <c r="R31" t="n">
-        <v>7142260</v>
+        <v>7142533</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,7 +3816,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119651696</v>
+        <v>119651694</v>
       </c>
       <c r="B32" t="n">
         <v>90580</v>
@@ -3862,10 +3856,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478181</v>
+        <v>477874</v>
       </c>
       <c r="R32" t="n">
-        <v>7142430</v>
+        <v>7142867</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,10 +3918,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119651694</v>
+        <v>119651645</v>
       </c>
       <c r="B33" t="n">
-        <v>90580</v>
+        <v>91254</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3936,25 +3930,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3964,10 +3958,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477874</v>
+        <v>478034</v>
       </c>
       <c r="R33" t="n">
-        <v>7142867</v>
+        <v>7142532</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4026,10 +4020,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119651706</v>
+        <v>119651676</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4042,21 +4036,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4066,10 +4060,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478162</v>
+        <v>478329</v>
       </c>
       <c r="R34" t="n">
-        <v>7142400</v>
+        <v>7142297</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4102,6 +4096,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4128,10 +4127,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119651678</v>
+        <v>119651696</v>
       </c>
       <c r="B35" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4144,21 +4143,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4168,10 +4167,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477860</v>
+        <v>478181</v>
       </c>
       <c r="R35" t="n">
-        <v>7143097</v>
+        <v>7142430</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4204,11 +4203,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4235,10 +4229,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651690</v>
+        <v>119651641</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>91254</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4247,25 +4241,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4275,10 +4269,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478032</v>
+        <v>477881</v>
       </c>
       <c r="R36" t="n">
-        <v>7142707</v>
+        <v>7142847</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4337,10 +4331,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119651639</v>
+        <v>119651680</v>
       </c>
       <c r="B37" t="n">
-        <v>90562</v>
+        <v>79608</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4353,21 +4347,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4377,10 +4371,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478102</v>
+        <v>477977</v>
       </c>
       <c r="R37" t="n">
-        <v>7142644</v>
+        <v>7142600</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4439,10 +4433,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119651680</v>
+        <v>119651706</v>
       </c>
       <c r="B38" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4455,21 +4449,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4479,10 +4473,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477977</v>
+        <v>478162</v>
       </c>
       <c r="R38" t="n">
-        <v>7142600</v>
+        <v>7142400</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4541,7 +4535,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119651641</v>
+        <v>119651646</v>
       </c>
       <c r="B39" t="n">
         <v>91254</v>
@@ -4581,10 +4575,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477881</v>
+        <v>478074</v>
       </c>
       <c r="R39" t="n">
-        <v>7142847</v>
+        <v>7142501</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4643,10 +4637,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119651645</v>
+        <v>119651690</v>
       </c>
       <c r="B40" t="n">
-        <v>91254</v>
+        <v>90580</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4655,25 +4649,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4683,10 +4677,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478034</v>
+        <v>478032</v>
       </c>
       <c r="R40" t="n">
-        <v>7142532</v>
+        <v>7142707</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4745,10 +4739,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119651669</v>
+        <v>119651698</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4761,21 +4755,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4785,10 +4779,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477624</v>
+        <v>477862</v>
       </c>
       <c r="R41" t="n">
-        <v>7142669</v>
+        <v>7142754</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4821,11 +4815,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4852,10 +4841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119651668</v>
+        <v>119651643</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4864,25 +4853,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4892,10 +4881,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477695</v>
+        <v>477621</v>
       </c>
       <c r="R42" t="n">
-        <v>7142939</v>
+        <v>7142895</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4928,11 +4917,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4959,10 +4943,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119651679</v>
+        <v>119651688</v>
       </c>
       <c r="B43" t="n">
-        <v>57326</v>
+        <v>90558</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4975,21 +4959,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4999,10 +4983,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477695</v>
+        <v>477825</v>
       </c>
       <c r="R43" t="n">
-        <v>7143155</v>
+        <v>7143049</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5035,11 +5019,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5066,10 +5045,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119651644</v>
+        <v>119651697</v>
       </c>
       <c r="B44" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5078,25 +5057,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5106,10 +5085,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477632</v>
+        <v>478297</v>
       </c>
       <c r="R44" t="n">
-        <v>7142733</v>
+        <v>7142499</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5168,10 +5147,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119651643</v>
+        <v>119651670</v>
       </c>
       <c r="B45" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5180,38 +5159,54 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477621</v>
+        <v>477861</v>
       </c>
       <c r="R45" t="n">
-        <v>7142895</v>
+        <v>7142701</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5270,10 +5265,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119651707</v>
+        <v>119651674</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5286,21 +5281,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5310,10 +5305,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478303</v>
+        <v>478153</v>
       </c>
       <c r="R46" t="n">
-        <v>7142341</v>
+        <v>7142438</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5346,6 +5341,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5372,10 +5372,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119651685</v>
+        <v>119651691</v>
       </c>
       <c r="B47" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5388,21 +5388,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478272</v>
+        <v>477857</v>
       </c>
       <c r="R47" t="n">
-        <v>7142513</v>
+        <v>7142825</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 575-2021 artfynd.xlsx
+++ b/artfynd/A 575-2021 artfynd.xlsx
@@ -4943,10 +4943,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119651688</v>
+        <v>119651691</v>
       </c>
       <c r="B43" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477825</v>
+        <v>477857</v>
       </c>
       <c r="R43" t="n">
-        <v>7143049</v>
+        <v>7142825</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5045,10 +5045,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119651697</v>
+        <v>119651688</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5061,21 +5061,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478297</v>
+        <v>477825</v>
       </c>
       <c r="R44" t="n">
-        <v>7142499</v>
+        <v>7143049</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5147,10 +5147,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119651670</v>
+        <v>119651697</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5163,50 +5163,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477861</v>
+        <v>478297</v>
       </c>
       <c r="R45" t="n">
-        <v>7142701</v>
+        <v>7142499</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5265,7 +5249,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119651674</v>
+        <v>119651670</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5298,17 +5282,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478153</v>
+        <v>477861</v>
       </c>
       <c r="R46" t="n">
-        <v>7142438</v>
+        <v>7142701</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5341,11 +5341,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5372,10 +5367,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119651691</v>
+        <v>119651674</v>
       </c>
       <c r="B47" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5388,21 +5383,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5412,10 +5407,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477857</v>
+        <v>478153</v>
       </c>
       <c r="R47" t="n">
-        <v>7142825</v>
+        <v>7142438</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5448,6 +5443,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 575-2021 artfynd.xlsx
+++ b/artfynd/A 575-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651669</v>
+        <v>119651678</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477624</v>
+        <v>477860</v>
       </c>
       <c r="R2" t="n">
-        <v>7142669</v>
+        <v>7143097</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651678</v>
+        <v>119651669</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477860</v>
+        <v>477624</v>
       </c>
       <c r="R3" t="n">
-        <v>7143097</v>
+        <v>7142669</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -4229,10 +4229,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651641</v>
+        <v>119651706</v>
       </c>
       <c r="B36" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4241,25 +4241,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477881</v>
+        <v>478162</v>
       </c>
       <c r="R36" t="n">
-        <v>7142847</v>
+        <v>7142400</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4331,10 +4331,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119651680</v>
+        <v>119651641</v>
       </c>
       <c r="B37" t="n">
-        <v>79608</v>
+        <v>91254</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4343,25 +4343,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477977</v>
+        <v>477881</v>
       </c>
       <c r="R37" t="n">
-        <v>7142600</v>
+        <v>7142847</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4433,10 +4433,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119651706</v>
+        <v>119651680</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4449,21 +4449,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478162</v>
+        <v>477977</v>
       </c>
       <c r="R38" t="n">
-        <v>7142400</v>
+        <v>7142600</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4943,10 +4943,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119651691</v>
+        <v>119651688</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477857</v>
+        <v>477825</v>
       </c>
       <c r="R43" t="n">
-        <v>7142825</v>
+        <v>7143049</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5045,10 +5045,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119651688</v>
+        <v>119651697</v>
       </c>
       <c r="B44" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5061,21 +5061,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477825</v>
+        <v>478297</v>
       </c>
       <c r="R44" t="n">
-        <v>7143049</v>
+        <v>7142499</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5147,10 +5147,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119651697</v>
+        <v>119651670</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5163,34 +5163,50 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478297</v>
+        <v>477861</v>
       </c>
       <c r="R45" t="n">
-        <v>7142499</v>
+        <v>7142701</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5249,7 +5265,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119651670</v>
+        <v>119651674</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5282,33 +5298,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477861</v>
+        <v>478153</v>
       </c>
       <c r="R46" t="n">
-        <v>7142701</v>
+        <v>7142438</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5341,6 +5341,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5367,10 +5372,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119651674</v>
+        <v>119651691</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5383,21 +5388,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5407,10 +5412,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478153</v>
+        <v>477857</v>
       </c>
       <c r="R47" t="n">
-        <v>7142438</v>
+        <v>7142825</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5443,11 +5448,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 575-2021 artfynd.xlsx
+++ b/artfynd/A 575-2021 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651638</v>
+        <v>119651709</v>
       </c>
       <c r="B4" t="n">
-        <v>87406</v>
+        <v>91128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478188</v>
+        <v>478183</v>
       </c>
       <c r="R4" t="n">
-        <v>7142387</v>
+        <v>7142390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119651644</v>
+        <v>119651638</v>
       </c>
       <c r="B5" t="n">
-        <v>91254</v>
+        <v>87406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477632</v>
+        <v>478188</v>
       </c>
       <c r="R5" t="n">
-        <v>7142733</v>
+        <v>7142387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651709</v>
+        <v>119651644</v>
       </c>
       <c r="B6" t="n">
-        <v>91128</v>
+        <v>91254</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478183</v>
+        <v>477632</v>
       </c>
       <c r="R6" t="n">
-        <v>7142390</v>
+        <v>7142733</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651665</v>
+        <v>119651679</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477656</v>
+        <v>477695</v>
       </c>
       <c r="R10" t="n">
-        <v>7143131</v>
+        <v>7143155</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,6 +1582,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651668</v>
+        <v>119651665</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477695</v>
+        <v>477656</v>
       </c>
       <c r="R11" t="n">
-        <v>7142939</v>
+        <v>7143131</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651679</v>
+        <v>119651668</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1758,7 +1758,7 @@
         <v>477695</v>
       </c>
       <c r="R12" t="n">
-        <v>7143155</v>
+        <v>7142939</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -4229,10 +4229,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651706</v>
+        <v>119651641</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4241,25 +4241,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478162</v>
+        <v>477881</v>
       </c>
       <c r="R36" t="n">
-        <v>7142400</v>
+        <v>7142847</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4331,10 +4331,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119651641</v>
+        <v>119651680</v>
       </c>
       <c r="B37" t="n">
-        <v>91254</v>
+        <v>79608</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4343,25 +4343,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477881</v>
+        <v>477977</v>
       </c>
       <c r="R37" t="n">
-        <v>7142847</v>
+        <v>7142600</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4433,10 +4433,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119651680</v>
+        <v>119651706</v>
       </c>
       <c r="B38" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4449,21 +4449,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477977</v>
+        <v>478162</v>
       </c>
       <c r="R38" t="n">
-        <v>7142600</v>
+        <v>7142400</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
